--- a/data/lookups/committente.xlsx
+++ b/data/lookups/committente.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\TOOLS\KNOWLEDGE SHARING\ProID\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Il mio Drive\TOOLS\KNOWLEDGE SHARING\ProID\data\lookups\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B98F8EDD-D5F8-4F16-B68D-05037F66FAD5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92930986-25B5-42F1-AC73-E6448A46C0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00488DC8-A6DA-48DE-B482-611741813DD3}"/>
+    <workbookView xWindow="31485" yWindow="1920" windowWidth="21600" windowHeight="11175" xr2:uid="{00488DC8-A6DA-48DE-B482-611741813DD3}"/>
   </bookViews>
   <sheets>
     <sheet name="Foglio1" sheetId="1" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="233" uniqueCount="233">
   <si>
     <t>value</t>
   </si>
@@ -553,6 +553,192 @@
   </si>
   <si>
     <t>ZZZ - Altro</t>
+  </si>
+  <si>
+    <t>CCIAA della BASILICATA (Matera-Potenza) </t>
+  </si>
+  <si>
+    <t>CCIAA della ROMAGNA (Forlì Cesena-Rimini) </t>
+  </si>
+  <si>
+    <t>CCIAA dell'EMILIA (Parma-Piacenza-Reggio Emilia)  </t>
+  </si>
+  <si>
+    <t>CCIAA di AGRIGENTO </t>
+  </si>
+  <si>
+    <t>CCIAA di ALESSANDRIA-ASTI </t>
+  </si>
+  <si>
+    <t>CCIAA di AREZZO-SIENA </t>
+  </si>
+  <si>
+    <t>CCIAA di BARI  </t>
+  </si>
+  <si>
+    <t>CCIAA di BERGAMO </t>
+  </si>
+  <si>
+    <t>CCIAA di BOLOGNA </t>
+  </si>
+  <si>
+    <t>CCIAA di BOLZANO </t>
+  </si>
+  <si>
+    <t>CCIAA di BRESCIA </t>
+  </si>
+  <si>
+    <t>CCIAA di BRINDISI-TARANTO  </t>
+  </si>
+  <si>
+    <t>CCIAA di CAGLIARI-ORISTANO  </t>
+  </si>
+  <si>
+    <t>CCIAA di CALTANISSETTA </t>
+  </si>
+  <si>
+    <t>CCIAA di CASERTA </t>
+  </si>
+  <si>
+    <t>CCIAA di CATANZARO-CROTONE-VIBO VALENTIA</t>
+  </si>
+  <si>
+    <t>CCIAA di CHIETI - PESCARA  </t>
+  </si>
+  <si>
+    <t>CCIAA di COMO-LECCO   </t>
+  </si>
+  <si>
+    <t>CCIAA di COSENZA  </t>
+  </si>
+  <si>
+    <t>CCIAA di CREMONA - MANTOVA - PAVIA</t>
+  </si>
+  <si>
+    <t>CCIAA di CUNEO</t>
+  </si>
+  <si>
+    <t>CCIAA di FERRARA-RAVENNA  </t>
+  </si>
+  <si>
+    <t>CCIAA di FIRENZE  </t>
+  </si>
+  <si>
+    <t>CCIAA di FOGGIA </t>
+  </si>
+  <si>
+    <t>CCIAA di FROSINONE- LATINA  </t>
+  </si>
+  <si>
+    <t>CCIAA di GENOVA  </t>
+  </si>
+  <si>
+    <t>CCIAA di GRAN SASSO D'ITALIA (L'Aquila-Teramo) </t>
+  </si>
+  <si>
+    <t>CCIAA di IRPINIA-SANNIO (Avellino-Benevento) </t>
+  </si>
+  <si>
+    <t>CCIAA di LECCE </t>
+  </si>
+  <si>
+    <t>CCIAA di MARCHE (Ancona-Ascoli Piceno-Fermo-Macerata-Pesaro Urbino)</t>
+  </si>
+  <si>
+    <t>CCIAA di MAREMMA E TIRRENO (Grosseto-Livorno)</t>
+  </si>
+  <si>
+    <t>CCIAA di MESSINA </t>
+  </si>
+  <si>
+    <t>CCIAA di MILANO MONZABRIANZA LODI</t>
+  </si>
+  <si>
+    <t>CCIAA di MODENA</t>
+  </si>
+  <si>
+    <t>CCIAA di MOLISE (Campobasso e Isernia)</t>
+  </si>
+  <si>
+    <t>CCIAA di MONTE ROSA, LAGHI, ALTO PIEMONTE (Biella-Novara-Vercelli-Verbania) </t>
+  </si>
+  <si>
+    <t>CCIAA di NAPOLI </t>
+  </si>
+  <si>
+    <t>CCIAA di NUORO </t>
+  </si>
+  <si>
+    <t>CCIAA di PADOVA   </t>
+  </si>
+  <si>
+    <t>CCIAA di PALERMO ed ENNA </t>
+  </si>
+  <si>
+    <t>CCIAA di PISTOIA - PRATO </t>
+  </si>
+  <si>
+    <t>CCIAA di PORDENONE- UDINE </t>
+  </si>
+  <si>
+    <t>CCIAA di REGGIO CALABRIA</t>
+  </si>
+  <si>
+    <t>CCIAA di RIETI - VITERBO</t>
+  </si>
+  <si>
+    <t>CCIAA di RIVIERE DI LIGURIA (Imperia-Savona-La Spezia)</t>
+  </si>
+  <si>
+    <t>CCIAA di ROMA</t>
+  </si>
+  <si>
+    <t>CCIAA di SALERNO </t>
+  </si>
+  <si>
+    <t>CCIAA di SASSARI </t>
+  </si>
+  <si>
+    <t>CCIAA di SONDRIO</t>
+  </si>
+  <si>
+    <t>CCIAA di SUD EST SICILIA (Catania-Ragusa-Siracusa) </t>
+  </si>
+  <si>
+    <t>CCIAA di TORINO </t>
+  </si>
+  <si>
+    <t>CCIAA di TOSCANA NORD OVEST (Lucca- Massa Carrara-Pisa) </t>
+  </si>
+  <si>
+    <t>CCIAA di TRAPANI</t>
+  </si>
+  <si>
+    <t>CCIAA di TRENTO </t>
+  </si>
+  <si>
+    <t>CCIAA di TREVISO - BELLUNO </t>
+  </si>
+  <si>
+    <t>CCIAA di UMBRIA (Perugia-Terni) </t>
+  </si>
+  <si>
+    <t>CCIAA di VARESE </t>
+  </si>
+  <si>
+    <t>CCIAA di VENEZIA GIULIA  (Gorizia-Trieste) </t>
+  </si>
+  <si>
+    <t>CCIAA di VENEZIA ROVIGO DELTA LAGUNARE </t>
+  </si>
+  <si>
+    <t>CCIAA di VERONA </t>
+  </si>
+  <si>
+    <t>CCIAA di VICENZA </t>
+  </si>
+  <si>
+    <t>CCIAA VALDOSTANA </t>
   </si>
 </sst>
 </file>
@@ -946,312 +1132,312 @@
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>15</v>
+        <v>171</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>125</v>
+        <v>172</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>54</v>
+        <v>173</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>174</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>175</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>10</v>
+        <v>176</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>13</v>
+        <v>177</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>18</v>
+        <v>178</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>179</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>22</v>
+        <v>180</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>24</v>
+        <v>181</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>26</v>
+        <v>182</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>29</v>
+        <v>183</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>32</v>
+        <v>184</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>34</v>
+        <v>185</v>
       </c>
     </row>
     <row r="17" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>36</v>
+        <v>186</v>
       </c>
     </row>
     <row r="18" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>40</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>43</v>
+        <v>188</v>
       </c>
     </row>
     <row r="20" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>46</v>
+        <v>189</v>
       </c>
     </row>
     <row r="21" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>48</v>
+        <v>190</v>
       </c>
     </row>
     <row r="22" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>52</v>
+        <v>191</v>
       </c>
     </row>
     <row r="23" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>58</v>
+        <v>192</v>
       </c>
     </row>
     <row r="24" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>61</v>
+        <v>193</v>
       </c>
     </row>
     <row r="25" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>63</v>
+        <v>194</v>
       </c>
     </row>
     <row r="26" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>65</v>
+        <v>195</v>
       </c>
     </row>
     <row r="27" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>68</v>
+        <v>196</v>
       </c>
     </row>
     <row r="28" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>70</v>
+        <v>197</v>
       </c>
     </row>
     <row r="29" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>74</v>
+        <v>198</v>
       </c>
     </row>
     <row r="30" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>78</v>
+        <v>199</v>
       </c>
     </row>
     <row r="31" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>80</v>
+        <v>200</v>
       </c>
     </row>
     <row r="32" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>82</v>
+        <v>201</v>
       </c>
     </row>
     <row r="33" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>85</v>
+        <v>202</v>
       </c>
     </row>
     <row r="34" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>87</v>
+        <v>203</v>
       </c>
     </row>
     <row r="35" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>89</v>
+        <v>204</v>
       </c>
     </row>
     <row r="36" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>91</v>
+        <v>205</v>
       </c>
     </row>
     <row r="37" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>93</v>
+        <v>206</v>
       </c>
     </row>
     <row r="38" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>98</v>
+        <v>207</v>
       </c>
     </row>
     <row r="39" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>101</v>
+        <v>208</v>
       </c>
     </row>
     <row r="40" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>103</v>
+        <v>209</v>
       </c>
     </row>
     <row r="41" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>105</v>
+        <v>210</v>
       </c>
     </row>
     <row r="42" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>108</v>
+        <v>211</v>
       </c>
     </row>
     <row r="43" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>111</v>
+        <v>212</v>
       </c>
     </row>
     <row r="44" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>114</v>
+        <v>213</v>
       </c>
     </row>
     <row r="45" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>116</v>
+        <v>214</v>
       </c>
     </row>
     <row r="46" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>119</v>
+        <v>215</v>
       </c>
     </row>
     <row r="47" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>123</v>
+        <v>216</v>
       </c>
     </row>
     <row r="48" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>128</v>
+        <v>217</v>
       </c>
     </row>
     <row r="49" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>130</v>
+        <v>218</v>
       </c>
     </row>
     <row r="50" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>132</v>
+        <v>219</v>
       </c>
     </row>
     <row r="51" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>134</v>
+        <v>220</v>
       </c>
     </row>
     <row r="52" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>138</v>
+        <v>221</v>
       </c>
     </row>
     <row r="53" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>140</v>
+        <v>222</v>
       </c>
     </row>
     <row r="54" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A54" t="s">
-        <v>142</v>
+        <v>223</v>
       </c>
     </row>
     <row r="55" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A55" t="s">
-        <v>144</v>
+        <v>224</v>
       </c>
     </row>
     <row r="56" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A56" t="s">
-        <v>146</v>
+        <v>225</v>
       </c>
     </row>
     <row r="57" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A57" t="s">
-        <v>150</v>
+        <v>226</v>
       </c>
     </row>
     <row r="58" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A58" t="s">
-        <v>155</v>
+        <v>227</v>
       </c>
     </row>
     <row r="59" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>157</v>
+        <v>228</v>
       </c>
     </row>
     <row r="60" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A60" t="s">
-        <v>161</v>
+        <v>229</v>
       </c>
     </row>
     <row r="61" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>164</v>
+        <v>230</v>
       </c>
     </row>
     <row r="62" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>166</v>
+        <v>231</v>
       </c>
     </row>
     <row r="63" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>153</v>
+        <v>232</v>
       </c>
     </row>
     <row r="64" spans="1:1" x14ac:dyDescent="0.35">
